--- a/guc/dist/20261025_創意模型_v0.1.1.xlsx
+++ b/guc/dist/20261025_創意模型_v0.1.1.xlsx
@@ -6805,7 +6805,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6929,7 +6929,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7016,7 +7016,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7096,7 +7096,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7317,7 +7317,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7467,7 +7467,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7617,7 +7617,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7776,7 +7776,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7900,7 +7900,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8156,7 +8156,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8277,7 +8277,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8398,7 +8398,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8519,7 +8519,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8640,7 +8640,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -43899,7 +43899,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/guc/dist/20261025_創意模型_v0.1.1.xlsx
+++ b/guc/dist/20261025_創意模型_v0.1.1.xlsx
@@ -11434,7 +11434,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
     </r>
     <r>
       <rPr>
@@ -11453,6 +11453,319 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E48</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Marvell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mk_oth_26</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科占其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（高值；份額加總檢查用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mediatek/dist/20261025_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.1.1.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!F45</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科模型高值（基準 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；世芯模型只有 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trainium </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">份額，其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">av_oth_27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Broadcom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（份額加總檢查用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">avgo/dist/20261025_Broadcom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
@@ -11472,8 +11785,11 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!E48</t>
-    </r>
+      <t xml:space="preserve">In!E54</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mv_oth_27</t>
   </si>
   <si>
     <r>
@@ -11493,21 +11809,333 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">占其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（份額加總檢查用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邁威爾模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E49</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mk_oth_27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科占其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（高值；份額加總檢查用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mediatek/dist/20261025_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聯發科模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.1.1.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!F46</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">av_oth_28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Broadcom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY2028</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（份額加總檢查用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">avgo/dist/20261025_Broadcom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">模型</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">mk_oth_26</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科占其他 </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In!E55</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mv_oth_28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Marvell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占其他 </t>
     </r>
     <r>
       <rPr>
@@ -11536,197 +12164,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CY2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（高值；份額加總檢查用）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mediatek/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!F45</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科模型高值（基準 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；世芯模型只有 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Trainium </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">份額，其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">av_oth_27</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Broadcom </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">占其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2027</t>
+      <t xml:space="preserve">CY2028</t>
     </r>
     <r>
       <rPr>
@@ -11747,119 +12185,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avgo/dist/20261025_Broadcom</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!E54</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">mv_oth_27</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Marvell </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">占其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（份額加總檢查用）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
     </r>
     <r>
       <rPr>
@@ -11878,333 +12204,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!E49</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">mk_oth_27</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科占其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（高值；份額加總檢查用）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mediatek/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">聯發科模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!F46</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">av_oth_28</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Broadcom </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">占其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2028</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（份額加總檢查用）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">avgo/dist/20261025_Broadcom</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">In!E55</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">mv_oth_28</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Marvell </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">占其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ASIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2028</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（份額加總檢查用）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邁威爾模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -43956,7 +43956,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">mrvl/dist/20261025_</t>
+      <t xml:space="preserve">mrvl/dist/20261026_</t>
     </r>
     <r>
       <rPr>
@@ -43975,7 +43975,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/guc/dist/20261025_創意模型_v0.1.1.xlsx
+++ b/guc/dist/20261025_創意模型_v0.1.1.xlsx
@@ -6786,26 +6786,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6910,26 +6910,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6997,26 +6997,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7077,26 +7077,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7298,26 +7298,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7448,26 +7448,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7598,26 +7598,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7757,26 +7757,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7881,26 +7881,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8137,26 +8137,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8258,26 +8258,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8379,26 +8379,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8500,26 +8500,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8621,26 +8621,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -43880,26 +43880,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
